--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,765 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25MVC</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>026078008681</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>3560000.0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25MVC</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>026078008681</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>4820000.0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MVC</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>026078008681</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>4988000.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MVC</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>026078008681</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>4992000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MTL</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>11019</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>037165003053</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1495200.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MTL</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>11020</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>037165003053</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>1490000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MTL</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>11075</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>037165003053</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>1145000.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MTL</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>037165003053</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>290000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MTH</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>077094004359</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>4950000.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MND</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>095194004728</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>4950000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MND</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>095194004728</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>4297000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -589,32 +589,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVC</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>026078008681</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -634,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1495200.0</v>
+        <v>4930000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1490000.0</v>
+        <v>1495200.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -772,7 +772,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1145000.0</v>
+        <v>1490000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -841,7 +841,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>290000.0</v>
+        <v>1145000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -865,32 +865,32 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>4950000.0</v>
+        <v>290000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -934,32 +934,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MTH</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>077094004359</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1048,14 +1048,83 @@
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
+        <v>4950000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MND</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>095194004728</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
         <v>4297000.0</v>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>4489500.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>3560000.0</v>
+        <v>4489500.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -377,57 +381,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>4820000.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +454,61 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>4988000.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,61 +527,65 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>4992000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -584,61 +600,65 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>4930000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -653,57 +673,61 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>527800.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1495200.0</v>
+        <v>527800.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -722,57 +746,61 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="L13" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1490000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -791,57 +819,61 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="L14" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1145000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -860,61 +892,65 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="L15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>290000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -929,61 +965,65 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="L16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>4950000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -998,57 +1038,61 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="L17" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>4950000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1067,64 +1111,1236 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>735000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>46792</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>46793</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>46794</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>527800.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>527800.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>46795</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>402500.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>402500.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>46796</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>493500.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>493500.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>46797</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>630000.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>630000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>46798</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>126000.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>126000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>46799</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>456450.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>456450.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MTT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
           <t>10/11/2025</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>095194004728</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="13" t="n">
-        <v>4297000.0</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0317887567</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>5712000.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>5712000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>260059</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>264157</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>267298</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>269619</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>270810</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>274708</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>278331</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>2142083.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>171367.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>3560000.0</v>
+        <v>2313450.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -382,42 +386,42 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K8" s="6"/>
@@ -427,7 +431,7 @@
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>4820000.0</v>
+        <v>2930000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +450,61 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>4800934.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>384075.0</v>
+      </c>
       <c r="N9" s="13" t="n">
-        <v>0.0</v>
+        <v>16566.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>4988000.0</v>
+        <v>5185009.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,57 +523,61 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>7314815.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>585185.0</v>
+      </c>
       <c r="N10" s="13" t="n">
-        <v>0.0</v>
+        <v>1085185.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>4992000.0</v>
+        <v>7900000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -584,17 +596,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -604,37 +616,41 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>2841058.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>227285.0</v>
+      </c>
       <c r="N11" s="13" t="n">
-        <v>0.0</v>
+        <v>273692.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>4930000.0</v>
+        <v>3068343.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -653,57 +669,61 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>1759259.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>140741.0</v>
+      </c>
       <c r="N12" s="13" t="n">
-        <v>0.0</v>
+        <v>259741.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1495200.0</v>
+        <v>1900000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -722,57 +742,61 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="L13" s="13" t="n">
+        <v>1476000.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>118080.0</v>
+      </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1490000.0</v>
+        <v>1594080.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -791,57 +815,61 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="L14" s="13" t="n">
+        <v>2847410.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>227793.0</v>
+      </c>
       <c r="N14" s="13" t="n">
-        <v>0.0</v>
+        <v>42150.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1145000.0</v>
+        <v>3075203.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -860,57 +888,61 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="L15" s="13" t="n">
+        <v>2499840.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>199987.0</v>
+      </c>
       <c r="N15" s="13" t="n">
-        <v>0.0</v>
+        <v>8160.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>290000.0</v>
+        <v>2699827.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -929,57 +961,61 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="L16" s="13" t="n">
+        <v>2812000.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>224960.0</v>
+      </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>1200000.0</v>
+        <v>3036960.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -998,57 +1034,61 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="L17" s="13" t="n">
+        <v>2760345.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>220828.0</v>
+      </c>
       <c r="N17" s="13" t="n">
-        <v>0.0</v>
+        <v>212555.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1432800.0</v>
+        <v>2981173.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1067,57 +1107,61 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="L18" s="13" t="n">
+        <v>8796296.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>703704.0</v>
+      </c>
       <c r="N18" s="13" t="n">
-        <v>0.0</v>
+        <v>1247704.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>4950000.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1136,57 +1180,61 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K19" s="6"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="L19" s="13" t="n">
+        <v>1677430.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>134194.0</v>
+      </c>
       <c r="N19" s="13" t="n">
-        <v>0.0</v>
+        <v>9570.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>4950000.0</v>
+        <v>1811624.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1205,64 +1253,2550 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>963676.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>77094.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>98924.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>1040770.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>11817</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>9333333.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>746667.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>1321467.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>1.008E7</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>7496</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>1418722.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>113498.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>43878.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>1532220.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>7594</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>4666667.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>373333.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>696733.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>5040000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>1802791.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>144223.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>21909.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>1947014.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>4777276.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>382182.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>85524.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>5159458.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>8439</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>1687200.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>134976.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>1822176.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>8792</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>3775706.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>302056.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>23694.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>4077762.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>8820</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>2462963.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>197037.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>363637.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>2660000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>8844</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>3148148.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>251852.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>475852.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>3400000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
           <t>10/11/2025</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>095194004728</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13" t="n">
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>4.3333333E7</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>3466667.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>3286667.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>4.68E7</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>9489</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>1779206.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>142336.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>44034.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>1921542.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>9490</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>2.172E7</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>1737600.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="O20" s="13" t="n">
-        <v>4297000.0</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="O32" s="13" t="n">
+        <v>2.34576E7</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>9528</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>4722222.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>377778.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>713778.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>5100000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>7486406.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>598912.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>241594.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>8085318.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>16484</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>3630555.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>290445.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>3921000.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>16485</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>2.7407408E7</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>2192592.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>2.96E7</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>19183</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>3782408.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>302592.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>4085000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>3240000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>7351852.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>588148.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>7940000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>7777778.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>622222.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>8400000.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>2.3333333E7</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>1866667.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>2.52E7</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>8888889.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>711111.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>9600000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>4.225E7</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>3380000.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>4.563E7</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>3.1194444E7</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>2495556.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>3.369E7</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>4.0736111E7</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>3258889.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>4.3995E7</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>1459722.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>116778.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>1576500.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>1262037.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>100963.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>1363000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>981482.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>78519.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>1060001.0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>1176389.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>94111.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>1270500.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>1496296.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>119704.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>1616000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>5.1161111E7</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>4092889.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>5.5254E7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>2333331.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>186666.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>2519997.0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>3136850.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>250948.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>3387798.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>2490756.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>199260.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>2690016.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -313,12 +313,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MCH</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -328,41 +328,41 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0313005616</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>2142083.0</v>
+        <v>4489500.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>171367.0</v>
+        <v>0.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>2313450.0</v>
+        <v>4489500.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -381,57 +381,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>584500.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>2930000.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -455,12 +459,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -470,41 +474,41 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>4800934.0</v>
+        <v>584500.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>384075.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>16566.0</v>
+        <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>5185009.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -528,60 +532,60 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>7314815.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>585185.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>1085185.0</v>
+        <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>7900000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -601,60 +605,60 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>2841058.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>227285.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="13" t="n">
-        <v>273692.0</v>
+        <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>3068343.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -674,56 +678,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>1759259.0</v>
+        <v>527800.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>140741.0</v>
+        <v>0.0</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>259741.0</v>
+        <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1900000.0</v>
+        <v>527800.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -747,56 +751,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>1476000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>118080.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1594080.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -820,56 +824,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>2847410.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>227793.0</v>
+        <v>0.0</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>42150.0</v>
+        <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>3075203.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -893,60 +897,60 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>2499840.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>199987.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>8160.0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>2699827.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -966,60 +970,60 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>2812000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>224960.0</v>
+        <v>0.0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>3036960.0</v>
+        <v>0.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -1039,56 +1043,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>2760345.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>220828.0</v>
+        <v>0.0</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>212555.0</v>
+        <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>2981173.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1112,56 +1116,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>8796296.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>703704.0</v>
+        <v>0.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>1247704.0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>9500000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1185,56 +1189,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>1677430.0</v>
+        <v>584500.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>134194.0</v>
+        <v>0.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>9570.0</v>
+        <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>1811624.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1258,56 +1262,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>963676.0</v>
+        <v>584500.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>77094.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>98924.0</v>
+        <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>1040770.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1331,56 +1335,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>9333333.0</v>
+        <v>527800.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>746667.0</v>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>1321467.0</v>
+        <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1.008E7</v>
+        <v>527800.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1404,56 +1408,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>1418722.0</v>
+        <v>402500.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>113498.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>43878.0</v>
+        <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>1532220.0</v>
+        <v>402500.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1477,56 +1481,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>46796</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>4666667.0</v>
+        <v>493500.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>373333.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>696733.0</v>
+        <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>5040000.0</v>
+        <v>493500.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1550,56 +1554,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>1802791.0</v>
+        <v>630000.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>144223.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>21909.0</v>
+        <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>1947014.0</v>
+        <v>630000.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1623,56 +1627,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>46798</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>4777276.0</v>
+        <v>126000.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>382182.0</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>85524.0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>5159458.0</v>
+        <v>126000.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1696,56 +1700,56 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>46799</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>1687200.0</v>
+        <v>456450.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>134976.0</v>
+        <v>0.0</v>
       </c>
       <c r="N26" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>1822176.0</v>
+        <v>456450.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1769,56 +1773,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>3775706.0</v>
+        <v>152150.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>302056.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="13" t="n">
-        <v>23694.0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>4077762.0</v>
+        <v>152150.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1842,56 +1846,56 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>2462963.0</v>
+        <v>5038080.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>197037.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="13" t="n">
-        <v>363637.0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>2660000.0</v>
+        <v>5038080.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1915,56 +1919,56 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MTT</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>0317887567</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY CỔ PHẦN SEPAY</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>3148148.0</v>
+        <v>5712000.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>251852.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="13" t="n">
-        <v>475852.0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>3400000.0</v>
+        <v>5712000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1988,56 +1992,56 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>260059</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>4.3333333E7</v>
+        <v>740741.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>3466667.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N30" s="13" t="n">
-        <v>3286667.0</v>
+        <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>4.68E7</v>
+        <v>800000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2061,56 +2065,56 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>264157</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>1779206.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>142336.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>44034.0</v>
+        <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>1921542.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2134,56 +2138,56 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>267298</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>2.172E7</v>
+        <v>740741.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1737600.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>2.34576E7</v>
+        <v>800000.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2207,56 +2211,56 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>269619</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>4722222.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>377778.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>713778.0</v>
+        <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>5100000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2280,56 +2284,56 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25MRV</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>270810</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>7486406.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>598912.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>241594.0</v>
+        <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>8085318.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2353,56 +2357,56 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25MBM</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>274708</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>3630555.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>290445.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>3921000.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2426,56 +2430,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25MBM</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>278331</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>2.7407408E7</v>
+        <v>740741.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>2192592.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>2.96E7</v>
+        <v>800000.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2499,56 +2503,56 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25MBM</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>281364</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>3782408.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>302592.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>4085000.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2572,56 +2576,56 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MDO</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>284965</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502397072</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>3000000.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>240000.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>3240000.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2645,56 +2649,54 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MMC</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>208589</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502545901</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>7351852.0</v>
+        <v>1577777.78</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>588148.0</v>
-      </c>
-      <c r="N39" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>126222.22</v>
+      </c>
+      <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>7940000.0</v>
+        <v>1704000.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2718,56 +2720,54 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MMC</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>208590</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502545901</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>7777778.0</v>
+        <v>659259.26</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>622222.0</v>
-      </c>
-      <c r="N40" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>52740.74</v>
+      </c>
+      <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>8400000.0</v>
+        <v>712000.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2791,56 +2791,54 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MMC</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>208591</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502545901</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>2.3333333E7</v>
+        <v>222222.22</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1866667.0</v>
-      </c>
-      <c r="N41" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>17777.78</v>
+      </c>
+      <c r="N41" s="13"/>
       <c r="O41" s="13" t="n">
-        <v>2.52E7</v>
+        <v>240000.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2864,56 +2862,54 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MMC</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>208592</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502545901</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>8888889.0</v>
+        <v>337962.96</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>711111.0</v>
-      </c>
-      <c r="N42" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>27037.04</v>
+      </c>
+      <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>9600000.0</v>
+        <v>365000.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2937,56 +2933,54 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MMC</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>208593</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502545901</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>4.225E7</v>
+        <v>243518.52</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>3380000.0</v>
-      </c>
-      <c r="N43" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>19481.48</v>
+      </c>
+      <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>4.563E7</v>
+        <v>263000.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2994,809 +2988,6 @@
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>C25MHN</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>13/11/2025</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>3502344144</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="13" t="n">
-        <v>3.1194444E7</v>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>2495556.0</v>
-      </c>
-      <c r="N44" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O44" s="13" t="n">
-        <v>3.369E7</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>C25MHN</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>18/11/2025</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>3502344144</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="13" t="n">
-        <v>4.0736111E7</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>3258889.0</v>
-      </c>
-      <c r="N45" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O45" s="13" t="n">
-        <v>4.3995E7</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>C25MDH</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>3502399055</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K46" s="6"/>
-      <c r="L46" s="13" t="n">
-        <v>1459722.0</v>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>116778.0</v>
-      </c>
-      <c r="N46" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O46" s="13" t="n">
-        <v>1576500.0</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>C25MDH</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>07/11/2025</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>3502399055</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K47" s="6"/>
-      <c r="L47" s="13" t="n">
-        <v>1262037.0</v>
-      </c>
-      <c r="M47" s="13" t="n">
-        <v>100963.0</v>
-      </c>
-      <c r="N47" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>1363000.0</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>C25MDH</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>08/11/2025</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>3502399055</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K48" s="6"/>
-      <c r="L48" s="13" t="n">
-        <v>981482.0</v>
-      </c>
-      <c r="M48" s="13" t="n">
-        <v>78519.0</v>
-      </c>
-      <c r="N48" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O48" s="13" t="n">
-        <v>1060001.0</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>C25MDH</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>14/11/2025</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>3502399055</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K49" s="6"/>
-      <c r="L49" s="13" t="n">
-        <v>1176389.0</v>
-      </c>
-      <c r="M49" s="13" t="n">
-        <v>94111.0</v>
-      </c>
-      <c r="N49" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O49" s="13" t="n">
-        <v>1270500.0</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>C25MDH</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>22/11/2025</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>3502399055</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K50" s="6"/>
-      <c r="L50" s="13" t="n">
-        <v>1496296.0</v>
-      </c>
-      <c r="M50" s="13" t="n">
-        <v>119704.0</v>
-      </c>
-      <c r="N50" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O50" s="13" t="n">
-        <v>1616000.0</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>C25MNB</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>2903</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>10/11/2025</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>3502437617</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K51" s="6"/>
-      <c r="L51" s="13" t="n">
-        <v>5.1161111E7</v>
-      </c>
-      <c r="M51" s="13" t="n">
-        <v>4092889.0</v>
-      </c>
-      <c r="N51" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O51" s="13" t="n">
-        <v>5.5254E7</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>C25MNL</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>05/11/2025</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>3502547930</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K52" s="6"/>
-      <c r="L52" s="13" t="n">
-        <v>2333331.0</v>
-      </c>
-      <c r="M52" s="13" t="n">
-        <v>186666.0</v>
-      </c>
-      <c r="N52" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O52" s="13" t="n">
-        <v>2519997.0</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>C25MNL</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>11/11/2025</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>3502547930</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K53" s="6"/>
-      <c r="L53" s="13" t="n">
-        <v>3136850.0</v>
-      </c>
-      <c r="M53" s="13" t="n">
-        <v>250948.0</v>
-      </c>
-      <c r="N53" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O53" s="13" t="n">
-        <v>3387798.0</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>C25MNL</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>18/11/2025</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>3502547930</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="K54" s="6"/>
-      <c r="L54" s="13" t="n">
-        <v>2490756.0</v>
-      </c>
-      <c r="M54" s="13" t="n">
-        <v>199260.0</v>
-      </c>
-      <c r="N54" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O54" s="13" t="n">
-        <v>2690016.0</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>1251691</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>4489500.0</v>
+        <v>68519.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>0.0</v>
+        <v>5481.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>4489500.0</v>
+        <v>74000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>1251948</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>584500.0</v>
+        <v>54630.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>0.0</v>
+        <v>4370.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>584500.0</v>
+        <v>59000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -454,61 +454,57 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MTD</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>034059004767</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>HỘ KINH DOANH ACCU THÀNH ĐẠT</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>584 Đường 30/4, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>584500.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>584500.0</v>
+        <v>650000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -527,65 +523,61 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MTP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>45217</t>
+          <t>721</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>077195008754</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>Hộ Kinh Doanh Thành Phát Computer</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>442/40 Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13" t="n">
-        <v>735000.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>735000.0</v>
+        <v>1550000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -600,65 +592,61 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MKN</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>080164010272</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>NHÀ NGHỈ KHÔI NGUYÊN</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Đường Số 1, KDC Thuận Đạo, Ấp Bến Lức 8, Xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>735000.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>735000.0</v>
+        <v>762300.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -673,61 +661,55 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MNY</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>080181017743</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>HỘ KINH DOANH SHOP HOA TƯƠI NHƯ Ý</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>56, Huỳnh Việt Thanh, Phường Long An, Tỉnh Tây Ninh.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>527800.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>527800.0</v>
+        <v>998000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -751,56 +733,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MAA</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>45220</t>
+          <t>579</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>1101981329</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH MTV TRÍ TÂM GROUP</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 10, Đường số 9, KDC Đường 10, Xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>735000.0</v>
+        <v>800000.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>0.0</v>
+        <v>64000.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>735000.0</v>
+        <v>864000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -824,56 +806,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MKS</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>1602058337</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI NHÀ HÀNG KHÁCH SẠN HÒA BÌNH</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 130 Trần Hưng Đạo, Phường Long Xuyên, Tỉnh An Giang, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>735000.0</v>
+        <v>981481.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0.0</v>
+        <v>78519.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>735000.0</v>
+        <v>1060000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -897,60 +879,60 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MNH</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>1602058337</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI NHÀ HÀNG KHÁCH SẠN HÒA BÌNH</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 130 Trần Hưng Đạo, Phường Long Xuyên, Tỉnh An Giang, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>0.0</v>
+        <v>346297.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>0.0</v>
+        <v>27703.0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.0</v>
+        <v>374000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -970,60 +952,60 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>45318</t>
+          <t>233624</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>0.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -1043,56 +1025,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>233636</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>735000.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>0.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>735000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1116,56 +1098,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>233715</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>735000.0</v>
+        <v>555556.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>0.0</v>
+        <v>44444.0</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>735000.0</v>
+        <v>600000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1189,56 +1171,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>46792</t>
+          <t>236064</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>584500.0</v>
+        <v>833333.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>0.0</v>
+        <v>66667.0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>584500.0</v>
+        <v>900000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1262,56 +1244,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>236066</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>584500.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>0.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>584500.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1335,56 +1317,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>242817</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>527800.0</v>
+        <v>1111111.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>0.0</v>
+        <v>88889.0</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>527800.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1408,56 +1390,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>242820</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>402500.0</v>
+        <v>833426.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>0.0</v>
+        <v>66674.0</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>402500.0</v>
+        <v>900100.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1481,12 +1463,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>258093</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1496,41 +1478,41 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>493500.0</v>
+        <v>185185.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>0.0</v>
+        <v>14815.0</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>493500.0</v>
+        <v>200000.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1554,12 +1536,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>258097</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1569,41 +1551,41 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>630000.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>0.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>630000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1627,56 +1609,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>263467</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>126000.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>0.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N25" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>126000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1700,56 +1682,56 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>263610</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>456450.0</v>
+        <v>555556.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>0.0</v>
+        <v>44444.0</v>
       </c>
       <c r="N26" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>456450.0</v>
+        <v>600000.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1773,56 +1755,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MMA</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>264003</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500565941</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>152150.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>0.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>152150.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1846,56 +1828,56 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MTY</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500866723</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ THÀNH ĐẠT</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>544B Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>5038080.0</v>
+        <v>3.461E7</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>0.0</v>
+        <v>2768800.0</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>5038080.0</v>
+        <v>3.73788E7</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1914,61 +1896,57 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MTT</t>
+          <t>C25MTK</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0317887567</t>
+          <t>3502268408</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ NHÀ HÀNG SUSHI TOKYO</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 215/3 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="13" t="n">
-        <v>5712000.0</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
       <c r="N29" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>5712000.0</v>
+        <v>2326954.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1992,56 +1970,54 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>260059</t>
+          <t>164012</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502296074</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>740741.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>59259.0</v>
-      </c>
-      <c r="N30" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>37037.0</v>
+      </c>
+      <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>800000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2065,56 +2041,54 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>264157</t>
+          <t>164538</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502296074</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>740741.0</v>
+        <v>185185.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>59259.0</v>
-      </c>
-      <c r="N31" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>14815.0</v>
+      </c>
+      <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>800000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2138,56 +2112,54 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>267298</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502296074</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>740741.0</v>
+        <v>1111111.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>59259.0</v>
-      </c>
-      <c r="N32" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>88889.0</v>
+      </c>
+      <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>800000.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2211,56 +2183,54 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>269619</t>
+          <t>166940</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502296074</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>462963.0</v>
+        <v>277778.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>22222.0</v>
+      </c>
+      <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>500000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2284,56 +2254,56 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502402082</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỒNG ĐỨC TRÍ</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>127/1 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>740741.0</v>
+        <v>305556.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>59259.0</v>
+        <v>24444.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>800000.0</v>
+        <v>330000.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2357,56 +2327,56 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>274708</t>
+          <t>77313</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502402082</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỒNG ĐỨC TRÍ</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>127/1 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>740741.0</v>
+        <v>305556.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>59259.0</v>
+        <v>24444.0</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>800000.0</v>
+        <v>330000.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2430,56 +2400,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502530052</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐẦU TƯ ẨM THỰC SEAVIEW VŨNG TÀU</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 49 Bùi Thiện Ngộ, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>740741.0</v>
+        <v>552500.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>59259.0</v>
+        <v>49000.0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>800000.0</v>
+        <v>601500.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2503,60 +2473,60 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MSD</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>281364</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502561491</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH DỊCH VỤ ĂN UỐNG HƯNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>16 Trần Đại Nghĩa, Khu Đô Thị Chí Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>740741.0</v>
+        <v>1753000.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>59259.0</v>
+        <v>149480.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>800000.0</v>
+        <v>1902480.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -2576,60 +2546,60 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MSD</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>284965</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3502561491</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH DỊCH VỤ ĂN UỐNG HƯNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>16 Trần Đại Nghĩa, Khu Đô Thị Chí Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>740741.0</v>
+        <v>0.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
@@ -2649,54 +2619,56 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MGO</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>208589</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3600899948-003</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>1577777.78</v>
+        <v>2654545.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>126222.22</v>
-      </c>
-      <c r="N39" s="13"/>
+        <v>265455.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O39" s="13" t="n">
-        <v>1704000.0</v>
+        <v>2920000.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2720,54 +2692,56 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MGO</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>208590</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3600899948-003</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>659259.26</v>
+        <v>99000.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>52740.74</v>
-      </c>
-      <c r="N40" s="13"/>
+        <v>7920.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O40" s="13" t="n">
-        <v>712000.0</v>
+        <v>106920.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2791,54 +2765,56 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MGO</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>208591</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3600899948-003</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>222222.22</v>
+        <v>3436364.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>17777.78</v>
-      </c>
-      <c r="N41" s="13"/>
+        <v>343636.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O41" s="13" t="n">
-        <v>240000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2862,54 +2838,54 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MGT</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>208592</t>
+          <t>164</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>4202000578</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ - KINH DOANH THÉP KIM THIÊN PHÁT</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Thôn Ninh Mã, Xã Đại Lãnh, Tỉnh Khánh Hòa, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>337962.96</v>
+        <v>3.6825472E7</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>27037.04</v>
+        <v>3682547.0</v>
       </c>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>365000.0</v>
+        <v>4.0508019E7</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2933,54 +2909,54 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MGT</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>208593</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>4202000578</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ - KINH DOANH THÉP KIM THIÊN PHÁT</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Thôn Ninh Mã, Xã Đại Lãnh, Tỉnh Khánh Hòa, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>243518.52</v>
+        <v>9.4502183E7</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>19481.48</v>
+        <v>9450218.0</v>
       </c>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>263000.0</v>
+        <v>1.03952401E8</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MHM</t>
+          <t>C25MTQ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1251691</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0110269067-014</t>
+          <t>0302478297</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+          <t>CÔNG TY TNHH TRẦN QUANG VIỆT NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>621 Xô Viết Nghệ Tĩnh, Phường Bình Thạnh, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>68519.0</v>
+        <v>4.8453701E7</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>5481.0</v>
+        <v>3876299.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>74000.0</v>
+        <v>5.233E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MHM</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1251948</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0110269067-014</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>54630.0</v>
+        <v>2142083.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>4370.0</v>
+        <v>171367.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>59000.0</v>
+        <v>2313450.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -459,42 +459,42 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MTD</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>034059004767</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ACCU THÀNH ĐẠT</t>
+          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>584 Đường 30/4, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K9" s="6"/>
@@ -504,7 +504,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>650000.0</v>
+        <v>2930000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -523,57 +523,61 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MTP</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>077195008754</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Thành Phát Computer</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>442/40 Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>4800934.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>384075.0</v>
+      </c>
       <c r="N10" s="13" t="n">
-        <v>0.0</v>
+        <v>16566.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1550000.0</v>
+        <v>5185009.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -592,57 +596,61 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MKN</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>080164010272</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>NHÀ NGHỈ KHÔI NGUYÊN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Đường Số 1, KDC Thuận Đạo, Ấp Bến Lức 8, Xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>7314815.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>585185.0</v>
+      </c>
       <c r="N11" s="13" t="n">
-        <v>0.0</v>
+        <v>1085185.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>762300.0</v>
+        <v>7900000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -661,55 +669,61 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MNY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>080181017743</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH SHOP HOA TƯƠI NHƯ Ý</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>56, Huỳnh Việt Thanh, Phường Long An, Tỉnh Tây Ninh.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>2841058.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>227285.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>273692.0</v>
+      </c>
       <c r="O12" s="13" t="n">
-        <v>998000.0</v>
+        <v>3068343.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -733,56 +747,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MAA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>1101981329</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV TRÍ TÂM GROUP</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 10, Đường số 9, KDC Đường 10, Xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>800000.0</v>
+        <v>1759259.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>64000.0</v>
+        <v>140741.0</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0.0</v>
+        <v>259741.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>864000.0</v>
+        <v>1900000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -806,56 +820,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MKS</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>1602058337</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI NHÀ HÀNG KHÁCH SẠN HÒA BÌNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 130 Trần Hưng Đạo, Phường Long Xuyên, Tỉnh An Giang, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>981481.0</v>
+        <v>1476000.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>78519.0</v>
+        <v>118080.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1060000.0</v>
+        <v>1594080.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -879,56 +893,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MNH</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>1602058337</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI NHÀ HÀNG KHÁCH SẠN HÒA BÌNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 130 Trần Hưng Đạo, Phường Long Xuyên, Tỉnh An Giang, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>346297.0</v>
+        <v>2847410.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>27703.0</v>
+        <v>227793.0</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>0.0</v>
+        <v>42150.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>374000.0</v>
+        <v>3075203.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -952,56 +966,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>233624</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>462963.0</v>
+        <v>2499840.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>37037.0</v>
+        <v>199987.0</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>0.0</v>
+        <v>8160.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>500000.0</v>
+        <v>2699827.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1025,56 +1039,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>233636</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>925926.0</v>
+        <v>2812000.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>74074.0</v>
+        <v>224960.0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1000000.0</v>
+        <v>3036960.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1098,56 +1112,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>233715</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>555556.0</v>
+        <v>2760345.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>44444.0</v>
+        <v>220828.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>0.0</v>
+        <v>212555.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>600000.0</v>
+        <v>2981173.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1171,56 +1185,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>236064</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>833333.0</v>
+        <v>8796296.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>66667.0</v>
+        <v>703704.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0.0</v>
+        <v>1247704.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>900000.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1244,56 +1258,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>236066</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>462963.0</v>
+        <v>1677430.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>37037.0</v>
+        <v>134194.0</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>0.0</v>
+        <v>9570.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>500000.0</v>
+        <v>1811624.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1317,56 +1331,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>242817</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>1111111.0</v>
+        <v>963676.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>88889.0</v>
+        <v>77094.0</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>0.0</v>
+        <v>98924.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1200000.0</v>
+        <v>1040770.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1390,60 +1404,60 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>242820</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>833426.0</v>
+        <v>9333333.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>66674.0</v>
+        <v>746667.0</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>0.0</v>
+        <v>1321467.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>900100.0</v>
+        <v>1.008E7</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -1463,56 +1477,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>258093</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>185185.0</v>
+        <v>3104052.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>14815.0</v>
+        <v>248324.0</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>0.0</v>
+        <v>15048.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>200000.0</v>
+        <v>3352376.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1536,56 +1550,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>258097</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>462963.0</v>
+        <v>3672365.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>37037.0</v>
+        <v>293789.0</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>0.0</v>
+        <v>33885.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>500000.0</v>
+        <v>3966154.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1609,56 +1623,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>263467</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>925926.0</v>
+        <v>739200.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>74074.0</v>
+        <v>59136.0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>0.0</v>
+        <v>100800.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>1000000.0</v>
+        <v>798336.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1682,60 +1696,60 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>263610</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>555556.0</v>
+        <v>-1407407.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>44444.0</v>
+        <v>-112593.0</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>0.0</v>
+        <v>-207793.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>600000.0</v>
+        <v>-1520000.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -1755,56 +1769,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MMA</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>264003</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3500565941</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN TRUNG THÀNH</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Số 1594 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>462963.0</v>
+        <v>2111111.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>37037.0</v>
+        <v>168889.0</v>
       </c>
       <c r="N27" s="13" t="n">
-        <v>0.0</v>
+        <v>311689.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>500000.0</v>
+        <v>2280000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1828,56 +1842,56 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MTY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3500866723</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ THÀNH ĐẠT</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>544B Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>3.461E7</v>
+        <v>2184634.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>2768800.0</v>
+        <v>174771.0</v>
       </c>
       <c r="N28" s="13" t="n">
-        <v>0.0</v>
+        <v>67566.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>3.73788E7</v>
+        <v>2359405.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1896,57 +1910,61 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MTK</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3502268408</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ NHÀ HÀNG SUSHI TOKYO</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 215/3 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
+      <c r="L29" s="13" t="n">
+        <v>3148148.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>251852.0</v>
+      </c>
       <c r="N29" s="13" t="n">
-        <v>0.0</v>
+        <v>475852.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>2326954.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1970,54 +1988,56 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>164012</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3502296074</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>462963.0</v>
+        <v>1418722.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="N30" s="13"/>
+        <v>113498.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>43878.0</v>
+      </c>
       <c r="O30" s="13" t="n">
-        <v>500000.0</v>
+        <v>1532220.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2041,54 +2061,56 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>164538</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3502296074</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>185185.0</v>
+        <v>4666667.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>14815.0</v>
-      </c>
-      <c r="N31" s="13"/>
+        <v>373333.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>696733.0</v>
+      </c>
       <c r="O31" s="13" t="n">
-        <v>200000.0</v>
+        <v>5040000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2112,54 +2134,56 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>165701</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3502296074</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>1111111.0</v>
+        <v>1802791.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>88889.0</v>
-      </c>
-      <c r="N32" s="13"/>
+        <v>144223.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>21909.0</v>
+      </c>
       <c r="O32" s="13" t="n">
-        <v>1200000.0</v>
+        <v>1947014.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2183,54 +2207,56 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>166940</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3502296074</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI VẬN TẢI NĂNG LƯỢNG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Tổ 5, Đường số 1, Thôn Tân Ninh, ấp Suối Tre, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>277778.0</v>
+        <v>4777276.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>22222.0</v>
-      </c>
-      <c r="N33" s="13"/>
+        <v>382182.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>85524.0</v>
+      </c>
       <c r="O33" s="13" t="n">
-        <v>300000.0</v>
+        <v>5159458.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2254,12 +2280,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>77174</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -2269,41 +2295,41 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3502402082</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỒNG ĐỨC TRÍ</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>127/1 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>305556.0</v>
+        <v>1687200.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>24444.0</v>
+        <v>134976.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>330000.0</v>
+        <v>1822176.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2327,56 +2353,56 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>77313</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3502402082</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỒNG ĐỨC TRÍ</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>127/1 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>305556.0</v>
+        <v>3775706.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>24444.0</v>
+        <v>302056.0</v>
       </c>
       <c r="N35" s="13" t="n">
-        <v>0.0</v>
+        <v>23694.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>330000.0</v>
+        <v>4077762.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2400,56 +2426,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502530052</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐẦU TƯ ẨM THỰC SEAVIEW VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 49 Bùi Thiện Ngộ, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>552500.0</v>
+        <v>2462963.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>49000.0</v>
+        <v>197037.0</v>
       </c>
       <c r="N36" s="13" t="n">
-        <v>0.0</v>
+        <v>363637.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>601500.0</v>
+        <v>2660000.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2473,60 +2499,60 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25MSD</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502561491</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ ĂN UỐNG HƯNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>16 Trần Đại Nghĩa, Khu Đô Thị Chí Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>1753000.0</v>
+        <v>3148148.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>149480.0</v>
+        <v>251852.0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0.0</v>
+        <v>475852.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>1902480.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -2546,60 +2572,60 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25MSD</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502561491</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ ĂN UỐNG HƯNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>16 Trần Đại Nghĩa, Khu Đô Thị Chí Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>0.0</v>
+        <v>4.3333333E7</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>0.0</v>
+        <v>3466667.0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>0.0</v>
+        <v>3286667.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>0.0</v>
+        <v>4.68E7</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
@@ -2619,56 +2645,56 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25MGO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3600899948-003</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>2654545.0</v>
+        <v>1779206.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>265455.0</v>
+        <v>142336.0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>0.0</v>
+        <v>44034.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>2920000.0</v>
+        <v>1921542.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2692,56 +2718,56 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25MGO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3600899948-003</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>99000.0</v>
+        <v>2.172E7</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>7920.0</v>
+        <v>1737600.0</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>106920.0</v>
+        <v>2.34576E7</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2765,56 +2791,56 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MGO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3600899948-003</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SONADEZI CHÂU ĐỨC - XÍ NGHIỆP GOLF CHÂU ĐỨC</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Sân Golf Châu Đức, Khu Công Nghiệp - Đô Thị Châu Đức, Đường Đ.02, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>3436364.0</v>
+        <v>4722222.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>343636.0</v>
+        <v>377778.0</v>
       </c>
       <c r="N41" s="13" t="n">
-        <v>0.0</v>
+        <v>713778.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>3780000.0</v>
+        <v>5100000.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2838,54 +2864,56 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25MGT</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>4202000578</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ - KINH DOANH THÉP KIM THIÊN PHÁT</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Thôn Ninh Mã, Xã Đại Lãnh, Tỉnh Khánh Hòa, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>3.6825472E7</v>
+        <v>7486406.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>3682547.0</v>
-      </c>
-      <c r="N42" s="13"/>
+        <v>598912.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>241594.0</v>
+      </c>
       <c r="O42" s="13" t="n">
-        <v>4.0508019E7</v>
+        <v>8085318.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2909,54 +2937,56 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MGT</t>
+          <t>C25MBM</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>4202000578</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ - KINH DOANH THÉP KIM THIÊN PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Thôn Ninh Mã, Xã Đại Lãnh, Tỉnh Khánh Hòa, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3501972322</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>9.4502183E7</v>
+        <v>3630555.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>9450218.0</v>
-      </c>
-      <c r="N43" s="13"/>
+        <v>290445.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O43" s="13" t="n">
-        <v>1.03952401E8</v>
+        <v>3921000.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2964,6 +2994,1612 @@
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>16485</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>2.7407408E7</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>2192592.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>2.96E7</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>19183</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>3782408.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>302592.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>4085000.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>3240000.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>7351852.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>588148.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>7940000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>7777778.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>622222.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>8400000.0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>2.3333333E7</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>1866667.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>2.52E7</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>8888889.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>711111.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>9600000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>4.225E7</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>3380000.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>4.563E7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>3.1194444E7</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>2495556.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>3.369E7</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>4.0736111E7</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>3258889.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>4.3995E7</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>1459722.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>116778.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>1576500.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>1262037.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>100963.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>1363000.0</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>981482.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>78519.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>1060001.0</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>1176389.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>94111.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>1270500.0</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>1496296.0</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>119704.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>1616000.0</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>1376389.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>110111.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>1486500.0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>5.1161111E7</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>4092889.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>5.5254E7</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>7.11378E7</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>5691024.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>7.6828824E7</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>2333331.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>186666.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>2519997.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>3136850.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>250948.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>3387798.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>2490756.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>199260.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>2690016.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MKL</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502553204</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI KIM LÂN</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8, Ấp 2, Xã Hòa Hội, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>4.537037E7</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>3629630.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>4.9E7</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MTQ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>0302478297</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH TRẦN QUANG VIỆT NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>621 Xô Viết Nghệ Tĩnh, Phường Bình Thạnh, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>4489500.0</v>
+        <v>4.8453701E7</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>0.0</v>
+        <v>3876299.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>4489500.0</v>
+        <v>5.233E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>584500.0</v>
+        <v>2142083.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>0.0</v>
+        <v>171367.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>584500.0</v>
+        <v>2313450.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -454,61 +454,57 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>584500.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>584500.0</v>
+        <v>2930000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -532,12 +528,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>45217</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -547,45 +543,45 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>735000.0</v>
+        <v>4800934.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>0.0</v>
+        <v>384075.0</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>0.0</v>
+        <v>16566.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>735000.0</v>
+        <v>5185009.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -605,60 +601,60 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>735000.0</v>
+        <v>7314815.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>0.0</v>
+        <v>585185.0</v>
       </c>
       <c r="N11" s="13" t="n">
-        <v>0.0</v>
+        <v>1085185.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>735000.0</v>
+        <v>7900000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -678,56 +674,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>527800.0</v>
+        <v>2841058.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>0.0</v>
+        <v>227285.0</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>0.0</v>
+        <v>273692.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>527800.0</v>
+        <v>3068343.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -751,56 +747,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>45220</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>735000.0</v>
+        <v>1759259.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>0.0</v>
+        <v>140741.0</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0.0</v>
+        <v>259741.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>735000.0</v>
+        <v>1900000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -824,56 +820,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>735000.0</v>
+        <v>1476000.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0.0</v>
+        <v>118080.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>735000.0</v>
+        <v>1594080.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -897,60 +893,60 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>0.0</v>
+        <v>2847410.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>0.0</v>
+        <v>227793.0</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>0.0</v>
+        <v>42150.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0.0</v>
+        <v>3075203.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -970,60 +966,60 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>45318</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>0.0</v>
+        <v>2499840.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0.0</v>
+        <v>199987.0</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>0.0</v>
+        <v>8160.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.0</v>
+        <v>2699827.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -1043,12 +1039,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1058,41 +1054,41 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>735000.0</v>
+        <v>2812000.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>0.0</v>
+        <v>224960.0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>735000.0</v>
+        <v>3036960.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1116,56 +1112,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>735000.0</v>
+        <v>2760345.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>0.0</v>
+        <v>220828.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>0.0</v>
+        <v>212555.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>735000.0</v>
+        <v>2981173.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1189,56 +1185,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>46792</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>584500.0</v>
+        <v>8796296.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>0.0</v>
+        <v>703704.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0.0</v>
+        <v>1247704.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>584500.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1262,56 +1258,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>584500.0</v>
+        <v>1677430.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>0.0</v>
+        <v>134194.0</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>0.0</v>
+        <v>9570.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>584500.0</v>
+        <v>1811624.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1335,56 +1331,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>527800.0</v>
+        <v>963676.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>0.0</v>
+        <v>77094.0</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>0.0</v>
+        <v>98924.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>527800.0</v>
+        <v>1040770.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1408,60 +1404,60 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>402500.0</v>
+        <v>9333333.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>0.0</v>
+        <v>746667.0</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>0.0</v>
+        <v>1321467.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>402500.0</v>
+        <v>1.008E7</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -1481,56 +1477,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>493500.0</v>
+        <v>3104052.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>0.0</v>
+        <v>248324.0</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>0.0</v>
+        <v>15048.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>493500.0</v>
+        <v>3352376.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1554,56 +1550,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>630000.0</v>
+        <v>3672365.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>0.0</v>
+        <v>293789.0</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>0.0</v>
+        <v>33885.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>630000.0</v>
+        <v>3966154.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1627,56 +1623,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>126000.0</v>
+        <v>739200.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>0.0</v>
+        <v>59136.0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>0.0</v>
+        <v>100800.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>126000.0</v>
+        <v>798336.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1700,60 +1696,60 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>456450.0</v>
+        <v>-1407407.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>0.0</v>
+        <v>-112593.0</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>0.0</v>
+        <v>-207793.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>456450.0</v>
+        <v>-1520000.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
@@ -1773,56 +1769,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>152150.0</v>
+        <v>2111111.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>0.0</v>
+        <v>168889.0</v>
       </c>
       <c r="N27" s="13" t="n">
-        <v>0.0</v>
+        <v>311689.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>152150.0</v>
+        <v>2280000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1846,56 +1842,56 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>5038080.0</v>
+        <v>2184634.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>0.0</v>
+        <v>174771.0</v>
       </c>
       <c r="N28" s="13" t="n">
-        <v>0.0</v>
+        <v>67566.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>5038080.0</v>
+        <v>2359405.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1919,56 +1915,56 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ Phần Phát Hành Sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>630000.0</v>
+        <v>3148148.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>0.0</v>
+        <v>251852.0</v>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0.0</v>
+        <v>475852.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>630000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>48937</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -2007,41 +2003,41 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ Phần Phát Hành Sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>402500.0</v>
+        <v>3163228.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>0.0</v>
+        <v>253058.0</v>
       </c>
       <c r="N30" s="13" t="n">
-        <v>0.0</v>
+        <v>73452.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>402500.0</v>
+        <v>3416286.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2065,12 +2061,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>48938</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2080,41 +2076,41 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ Phần Phát Hành Sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>560000.0</v>
+        <v>166104.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>0.0</v>
+        <v>13288.0</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>0.0</v>
+        <v>18456.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>560000.0</v>
+        <v>179392.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2138,56 +2134,56 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25MEX</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>48939</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>29/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>0304132047</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ Phần Phát Hành Sách TPHCM - Fahasa</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>644700.0</v>
+        <v>6296296.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>0.0</v>
+        <v>503704.0</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>0.0</v>
+        <v>951704.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>644700.0</v>
+        <v>6800000.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2211,47 +2207,47 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25MTT</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>29/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0317887567</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>5712000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>0.0</v>
@@ -2260,7 +2256,7 @@
         <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>5712000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2279,57 +2275,61 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25MSV</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>30/11/2025</t>
+          <t>29/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>077086000902</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH MUA BÁN MÁY VĂN PHÒNG SAO VIỆT</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>31 đường Bắc Sơn, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K34" s="6"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
+      <c r="L34" s="13" t="n">
+        <v>3168000.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>253440.0</v>
+      </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>7200000.0</v>
+        <v>3421440.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>260059</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2368,41 +2368,41 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>740741.0</v>
+        <v>1418722.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>59259.0</v>
+        <v>113498.0</v>
       </c>
       <c r="N35" s="13" t="n">
-        <v>0.0</v>
+        <v>43878.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>800000.0</v>
+        <v>1532220.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2426,56 +2426,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>264157</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>740741.0</v>
+        <v>4666667.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>59259.0</v>
+        <v>373333.0</v>
       </c>
       <c r="N36" s="13" t="n">
-        <v>0.0</v>
+        <v>696733.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>800000.0</v>
+        <v>5040000.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2499,56 +2499,56 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>267298</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>740741.0</v>
+        <v>1802791.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>59259.0</v>
+        <v>144223.0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0.0</v>
+        <v>21909.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>800000.0</v>
+        <v>1947014.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2572,56 +2572,56 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>269619</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>462963.0</v>
+        <v>4777276.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>37037.0</v>
+        <v>382182.0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>0.0</v>
+        <v>85524.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>500000.0</v>
+        <v>5159458.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2645,56 +2645,56 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>740741.0</v>
+        <v>1687200.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>59259.0</v>
+        <v>134976.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>800000.0</v>
+        <v>1822176.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2718,56 +2718,56 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>274708</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>740741.0</v>
+        <v>3775706.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>59259.0</v>
+        <v>302056.0</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>0.0</v>
+        <v>23694.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>800000.0</v>
+        <v>4077762.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2791,56 +2791,56 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>740741.0</v>
+        <v>2462963.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>59259.0</v>
+        <v>197037.0</v>
       </c>
       <c r="N41" s="13" t="n">
-        <v>0.0</v>
+        <v>363637.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>800000.0</v>
+        <v>2660000.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2864,56 +2864,56 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>281364</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>740741.0</v>
+        <v>3148148.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>59259.0</v>
+        <v>251852.0</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0.0</v>
+        <v>475852.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>800000.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2937,56 +2937,56 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>284965</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>740741.0</v>
+        <v>4.3333333E7</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>59259.0</v>
+        <v>3466667.0</v>
       </c>
       <c r="N43" s="13" t="n">
-        <v>0.0</v>
+        <v>3286667.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>800000.0</v>
+        <v>4.68E7</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -3010,56 +3010,56 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>287143</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách mạng tháng tám, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>740741.0</v>
+        <v>1779206.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>59259.0</v>
+        <v>142336.0</v>
       </c>
       <c r="N44" s="13" t="n">
-        <v>0.0</v>
+        <v>44034.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>800000.0</v>
+        <v>1921542.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3083,54 +3083,56 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>208589</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>1577777.78</v>
+        <v>2.172E7</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>126222.22</v>
-      </c>
-      <c r="N45" s="13"/>
+        <v>1737600.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O45" s="13" t="n">
-        <v>1704000.0</v>
+        <v>2.34576E7</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3154,54 +3156,56 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>208590</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>659259.26</v>
+        <v>4722222.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>52740.74</v>
-      </c>
-      <c r="N46" s="13"/>
+        <v>377778.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>713778.0</v>
+      </c>
       <c r="O46" s="13" t="n">
-        <v>712000.0</v>
+        <v>5100000.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3225,54 +3229,56 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>208591</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>222222.22</v>
+        <v>7486406.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>17777.78</v>
-      </c>
-      <c r="N47" s="13"/>
+        <v>598912.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>241594.0</v>
+      </c>
       <c r="O47" s="13" t="n">
-        <v>240000.0</v>
+        <v>8085318.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3296,54 +3302,56 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MBM</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>208592</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>337962.96</v>
+        <v>3630555.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>27037.04</v>
-      </c>
-      <c r="N48" s="13"/>
+        <v>290445.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O48" s="13" t="n">
-        <v>365000.0</v>
+        <v>3921000.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3367,54 +3375,56 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C25MMC</t>
+          <t>C25MBM</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>208593</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3502545901</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>243518.52</v>
+        <v>2.7407408E7</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>19481.48</v>
-      </c>
-      <c r="N49" s="13"/>
+        <v>2192592.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O49" s="13" t="n">
-        <v>263000.0</v>
+        <v>2.96E7</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3422,6 +3432,1758 @@
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>19183</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>3782408.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>302592.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>4085000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MHT</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>29/11/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502324074</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>6.9972E8</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>6.9972E7</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>7.69692E8</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>3240000.0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>7351852.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>588148.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>7940000.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>7777778.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>622222.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>8400000.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>2.3333333E7</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>1866667.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>2.52E7</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>8888889.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>711111.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>9600000.0</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>4.225E7</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>3380000.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>4.563E7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>3.1194444E7</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>2495556.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>3.369E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>4.0736111E7</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>3258889.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>4.3995E7</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>6175926.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>494074.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>6670000.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>1459722.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>116778.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>1576500.0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>1262037.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>100963.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>1363000.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>981482.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>78519.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>1060001.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>1176389.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>94111.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>1270500.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>1496296.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>119704.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>1616000.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>1376389.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>110111.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>1486500.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13" t="n">
+        <v>5.1161111E7</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>4092889.0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>5.5254E7</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="13" t="n">
+        <v>7.11378E7</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>5691024.0</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>7.6828824E7</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>29/11/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13" t="n">
+        <v>370800.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>29664.0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>400464.0</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13" t="n">
+        <v>2333331.0</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>186666.0</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>2519997.0</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13" t="n">
+        <v>3136850.0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>250948.0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>3387798.0</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13" t="n">
+        <v>2490756.0</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>199260.0</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>2690016.0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C25MKL</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502553204</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI KIM LÂN</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8, Ấp 2, Xã Hòa Hội, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13" t="n">
+        <v>4.537037E7</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>3629630.0</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>4.9E7</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
